--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XX/LTAIPT_A63F20.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="403">
   <si>
     <t>48969</t>
   </si>
@@ -181,34 +181,34 @@
     <t>Nombre del trámite</t>
   </si>
   <si>
-    <t>Descripción de trámite</t>
-  </si>
-  <si>
-    <t>Tipo de usuario y/o población objetivo</t>
+    <t>Descripción de trámite (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Tipo de población usuaria y/o población objetivo (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Modalidad del trámite</t>
   </si>
   <si>
-    <t>Hipervínculo a los requisitos para llevar a cabo el trámite</t>
-  </si>
-  <si>
-    <t>Documentos requeridos, en su caso</t>
+    <t>Hipervínculo a los requisitos para llevar a cabo el trámite (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Documentos requeridos, en su caso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Hipervínculo al/los formatos respectivos</t>
   </si>
   <si>
-    <t>Última fecha de publicación en el medio de difusión</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Última fecha de publicación en el medio de difusión</t>
   </si>
   <si>
     <t>Tiempo de respuesta por parte del sujeto Obligado</t>
   </si>
   <si>
-    <t>Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
-  </si>
-  <si>
-    <t>Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
   </si>
   <si>
     <t>Vigencia de los resultados del trámite</t>
@@ -218,7 +218,7 @@
 Tabla_436126</t>
   </si>
   <si>
-    <t>Monto de los derechos o aprovechamientos aplicables, en su caso</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Monto de los derechos o aprovechamientos aplicables, en su caso</t>
   </si>
   <si>
     <t>Sustento legal para su cobro</t>
@@ -231,10 +231,10 @@
     <t>Fundamento jurídico-administrativo de la existencia del trámite</t>
   </si>
   <si>
-    <t>Derechos del usuario</t>
-  </si>
-  <si>
-    <t>Información adicional del trámite, en su caso</t>
+    <t>Derechos de la persona usuaria ante la negativa o la falta de respuesta (especificar si aplica la afirmativa o negativa ficta) (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Información adicional del trámite, en su caso (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Medio que permita el envío de consultas y documentos 
@@ -260,25 +260,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>5D17E24B97F3CD069488054F95B7E009</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Duplicado de Certificado de Terminación de Estudios</t>
   </si>
   <si>
-    <t>Documento que acredita que el alumno aprobó en su totalidad las Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Ex-alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+    <t>Documento que acredita que los y las estudiantes aprobaron en su totalidad las Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Ex-estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
     <t>Presencial</t>
@@ -299,49 +290,130 @@
     <t>Quince días hábiles</t>
   </si>
   <si>
-    <t>Ver nota</t>
+    <t/>
+  </si>
+  <si>
+    <t>Permanente</t>
+  </si>
+  <si>
+    <t>8125242</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III el Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción III. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción I, Fracción VIII</t>
+  </si>
+  <si>
+    <t>Queja ante el Órgano de Control Interno del Sujeto Obligado</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>Revalidación de Estudios por Semestre</t>
+  </si>
+  <si>
+    <t>Procedimiento administrativo que se inicia a petición del aspirante a estudiante que cuenta con estudios parciales de Educación Media Superior realizados en instituciones del Sistema Educativo Nacional, y/o con certificado de competencia laboral con el fin de que se equiparen sus estudios a los del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>No adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, Certificado Parcial de la Institución de origen (original y dos copias), Certificado de Secundaria (original y dos copias), Acta de Nacimiento (original y dos copias), Clave Única de Registro de Población (original y dos copias) , Número de Seguridad Social Instituto Mexicano del Seguro Social (original y dos copias), Formato de baja de Seguro Instituto Mexicano del Seguo Social de la escuela anterior (original y dos copias), Comprobante de domicilio (original y dos copias), Copia de recibo de pago por semestres revalidados</t>
+  </si>
+  <si>
+    <t>Tres días hábiles</t>
   </si>
   <si>
     <t>Por el semestre</t>
   </si>
   <si>
-    <t>4826109</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III el Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción III. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV</t>
-  </si>
-  <si>
-    <t>Queja ante la Contraloría del Ejecutivo del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Certificado de Terminación de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>44155382C6549CAAAC1F2F59FC9BC094</t>
+    <t>8125243</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción VII. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción IV</t>
+  </si>
+  <si>
+    <t>Certificado Completo de Estudios</t>
+  </si>
+  <si>
+    <t>Documento oficial que expide el Colegio de Bachilleres del Estado de Tlaxcala con el que se otorga el reconocimiento oficial a la acreditación de Unidades de Aprendizaje Curricular</t>
+  </si>
+  <si>
+    <t>Estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos (incluye pago de paquete de fin de cursos),  seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, dos fotografías tamaño diploma</t>
+  </si>
+  <si>
+    <t>8125237</t>
+  </si>
+  <si>
+    <t>Certificado Parcial de Estudios</t>
+  </si>
+  <si>
+    <t>Documento que acredita que los y las estudiantes cursaron Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Solicitud de Trámite (proporcionado en el plantel donde cursó), Pago de Derechos, Productos y Aprovechamientos, seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CERTIFICADO%20PARCIAL%20DE%20ESTUDIOS.pdf</t>
+  </si>
+  <si>
+    <t>8125238</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Constancia de Calificaciones</t>
+  </si>
+  <si>
+    <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CONSTANCIA%20DE%20CALIFICACIONES.pdf</t>
+  </si>
+  <si>
+    <t>Un día  hábil</t>
+  </si>
+  <si>
+    <t>8125239</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción I</t>
+  </si>
+  <si>
+    <t>Constancia de Estudios</t>
+  </si>
+  <si>
+    <t>Documento que emite el Director del Plantel del Colegio de Bachilleres del Estado de Tlaxcala, en el que se manifiesta que los y las estudiantes se encuentras inscritos/as</t>
+  </si>
+  <si>
+    <t>8125240</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>Duplicado de Carta de Buena Conducta</t>
   </si>
   <si>
-    <t>Documento que acredita haber mostrado buena conducta como alumno del Colegio de Bachilleres del Estado Tlaxcala</t>
-  </si>
-  <si>
-    <t>Alumnos o ex-alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+    <t>Documento que acredita haber mostrado buena conducta como estudiante del Colegio de Bachilleres del Estado Tlaxcala</t>
+  </si>
+  <si>
+    <t>Estudiantes o ex-estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
     <t>Solicitud de Trámite (proporcionada en el plantel donde cursó), Pago de Derechos, Productos y Aprovechamientos</t>
@@ -350,130 +422,61 @@
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/DUPLICADO%20DE%20CARTA%20DE%20BUENA%20CONDUCTA.pdf</t>
   </si>
   <si>
-    <t>Un día  hábil</t>
-  </si>
-  <si>
-    <t>4826108</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción IV</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Duplicado de Carta de Buena Conducta). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>BEC401120FAEB9FF2C50DCE221EF5EA8</t>
-  </si>
-  <si>
-    <t>Constancia de Estudios</t>
-  </si>
-  <si>
-    <t>Documento que emite el Director del Plantel del Colegio de Bachilleres del Estado de Tlaxcala, en el que se manifiesta que un alumno se encuentra inscrito</t>
-  </si>
-  <si>
-    <t>Alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>4826107</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>0D3DDBBC367407C9BA925D19CDA0D592</t>
-  </si>
-  <si>
-    <t>Revalidación de Estudios por Semestre</t>
-  </si>
-  <si>
-    <t>Procedimiento administrativo que se inicia a petición del aspirante a alumno que cuenta con estudios parciales de Educación Media Superior realizados en instituciones del Sistema Educativo Nacional, y/o con certificado de competencia laboral con el fin de que se equiparen sus estudios a los del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>No adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, Certificado Parcial de la Institución de origen (original y dos copias), Certificado de Secundaria (original y dos copias), Acta de Nacimiento (original y dos copias), Clave Única de Registro de Población (original y dos copias) , Número de Seguridad Social Instituto Mexicano del Seguro Social (original y dos copias), Formato de baja de Seguro Instituto Mexicano del Seguo Social de la escuela anterior (original y dos copias), Comprobante de domicilio (original y dos copias), Copia de recibo de pago por semestres revalidados</t>
-  </si>
-  <si>
-    <t>Tres días hábiles</t>
-  </si>
-  <si>
-    <t>4826110</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción VII. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Revalidación de Estudios por Semestre.  El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Revalidación de Estudios por Semestre). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>221248E1E6974CAC7C9FA0C18BDE608A</t>
-  </si>
-  <si>
-    <t>Constancia de Calificaciones</t>
-  </si>
-  <si>
-    <t>Documento que acredita que el alumno cursó Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CONSTANCIA%20DE%20CALIFICACIONES.pdf</t>
-  </si>
-  <si>
-    <t>4826106</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Constancia de Calificaciones). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>0FF321B53F5D36BEA49B64EC1688F6D4</t>
-  </si>
-  <si>
-    <t>Certificado Parcial de Estudios</t>
-  </si>
-  <si>
-    <t>Solicitud de Trámite (proporcionado en el plantel donde cursó), Pago de Derechos, Productos y Aprovechamientos, seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/CERTIFICADO%20PARCIAL%20DE%20ESTUDIOS.pdf</t>
-  </si>
-  <si>
-    <t>4826105</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Parcial de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>C15736DE8DD26ACE260A066D9F0ED0AC</t>
-  </si>
-  <si>
-    <t>Certificado Completo de Estudios</t>
-  </si>
-  <si>
-    <t>Documento oficial que expide el Colegio de Bachilleres del Estado de Tlaxcala con el que se otorga el reconocimiento oficial a la acreditación de Unidades de Aprendizaje Curricular</t>
-  </si>
-  <si>
-    <t>Solicitud de Trámite (proporcionada en el plantel donde cursa), Pago de Derechos, Productos y Aprovechamientos (incluye pago de paquete de fin de cursos),  seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, dos fotografías tamaño diploma</t>
-  </si>
-  <si>
-    <t>4826104</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Certificado Completo de Estudios. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Certificado Completo de Estudios). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Medio que permita el envío de consultas y documentos.</t>
+    <t>8125241</t>
+  </si>
+  <si>
+    <t>5FA808317F5E6B76CD1ABF7845E5449E</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>8502271</t>
+  </si>
+  <si>
+    <t>23/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
+  </si>
+  <si>
+    <t>56608D6182FD5FFD27D213291ABDAD70</t>
+  </si>
+  <si>
+    <t>8502274</t>
+  </si>
+  <si>
+    <t>DEACD13920D4D4BA6CC3C2130F1D4B7E</t>
+  </si>
+  <si>
+    <t>8502268</t>
+  </si>
+  <si>
+    <t>4638FE8B3E06B0FD0186D88C629B47AB</t>
+  </si>
+  <si>
+    <t>8502269</t>
+  </si>
+  <si>
+    <t>00CEE97322ABBF36D888432A4FD8F3FC</t>
+  </si>
+  <si>
+    <t>8502270</t>
+  </si>
+  <si>
+    <t>FD2BA58A7E5E188668838835A1B53A0A</t>
+  </si>
+  <si>
+    <t>8502272</t>
+  </si>
+  <si>
+    <t>4B5726C38ACFF53D7A2787D59C388AC4</t>
+  </si>
+  <si>
+    <t>8502273</t>
   </si>
   <si>
     <t>9</t>
@@ -590,7 +593,7 @@
     <t>Horario de atención(días y horas)</t>
   </si>
   <si>
-    <t>FB2115CFBB440146AA054253D1D10D6F</t>
+    <t>E621B4F9309A3370627EF8D6443EAE38</t>
   </si>
   <si>
     <t>Control Escolar de cada uno de los 24 planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
@@ -629,13 +632,7 @@
     <t>Lunes a viernes de 8:30 a 17:30 horas</t>
   </si>
   <si>
-    <t>FB2115CFBB44014609103D05A0949F13</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5F0857079D1D4A58C</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146A16DDE16C23C1F2F</t>
+    <t>E255390FE79E15E70CE1C32BD7B24BB6</t>
   </si>
   <si>
     <t>Dirección Administrativa</t>
@@ -647,114 +644,144 @@
     <t>S/N</t>
   </si>
   <si>
+    <t>Panotla</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>90150</t>
+  </si>
+  <si>
+    <t>2464628521</t>
+  </si>
+  <si>
+    <t>Dir.Administrativa@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>10E46DE8C1834182A1107956DFE43E0F</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1E2163AE853DCFFF3</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1156C6E750E2CE416</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD17006FB5A9DB93D0E</t>
+  </si>
+  <si>
+    <t>E621B4F9309A337037CD5BB7F36E04E3</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F827BE79461A44FCBA4</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A2752752D7C9C7DB04</t>
+  </si>
+  <si>
+    <t>3A442F186DE26B0E1696F1FEDB228945</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C03DD4886423918E8</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5CE30634745190ED7C</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F8287BB59AC65268CB1</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F822B389E244966754A</t>
+  </si>
+  <si>
+    <t>Carretera</t>
+  </si>
+  <si>
+    <t>Privada</t>
+  </si>
+  <si>
+    <t>Eje vial</t>
+  </si>
+  <si>
+    <t>Circunvalación</t>
+  </si>
+  <si>
+    <t>Brecha</t>
+  </si>
+  <si>
+    <t>Diagonal</t>
+  </si>
+  <si>
+    <t>Corredor</t>
+  </si>
+  <si>
+    <t>Circuito</t>
+  </si>
+  <si>
+    <t>Pasaje</t>
+  </si>
+  <si>
+    <t>Vereda</t>
+  </si>
+  <si>
+    <t>Calzada</t>
+  </si>
+  <si>
+    <t>Viaducto</t>
+  </si>
+  <si>
+    <t>Prolongación</t>
+  </si>
+  <si>
+    <t>Boulevard</t>
+  </si>
+  <si>
+    <t>Peatonal</t>
+  </si>
+  <si>
+    <t>Retorno</t>
+  </si>
+  <si>
+    <t>Camino</t>
+  </si>
+  <si>
+    <t>Callejón</t>
+  </si>
+  <si>
+    <t>Cerrada</t>
+  </si>
+  <si>
+    <t>Ampliación</t>
+  </si>
+  <si>
+    <t>Continuación</t>
+  </si>
+  <si>
+    <t>Terracería</t>
+  </si>
+  <si>
+    <t>Andador</t>
+  </si>
+  <si>
+    <t>Periférico</t>
+  </si>
+  <si>
+    <t>Avenida</t>
+  </si>
+  <si>
+    <t>Aeropuerto</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>Cantón</t>
+  </si>
+  <si>
     <t>Ciudad</t>
   </si>
   <si>
-    <t>Panotla</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2464628521</t>
-  </si>
-  <si>
-    <t>Dir.Administrativa@cobatlaxcala.edu.mx</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF56A67A33217DF80AE</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271DE0D5BE9ADE31727</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D127153249C5697510FAD</t>
-  </si>
-  <si>
-    <t>Carretera</t>
-  </si>
-  <si>
-    <t>Privada</t>
-  </si>
-  <si>
-    <t>Eje vial</t>
-  </si>
-  <si>
-    <t>Circunvalación</t>
-  </si>
-  <si>
-    <t>Brecha</t>
-  </si>
-  <si>
-    <t>Diagonal</t>
-  </si>
-  <si>
-    <t>Corredor</t>
-  </si>
-  <si>
-    <t>Circuito</t>
-  </si>
-  <si>
-    <t>Pasaje</t>
-  </si>
-  <si>
-    <t>Vereda</t>
-  </si>
-  <si>
-    <t>Calzada</t>
-  </si>
-  <si>
-    <t>Viaducto</t>
-  </si>
-  <si>
-    <t>Prolongación</t>
-  </si>
-  <si>
-    <t>Boulevard</t>
-  </si>
-  <si>
-    <t>Peatonal</t>
-  </si>
-  <si>
-    <t>Retorno</t>
-  </si>
-  <si>
-    <t>Camino</t>
-  </si>
-  <si>
-    <t>Callejón</t>
-  </si>
-  <si>
-    <t>Cerrada</t>
-  </si>
-  <si>
-    <t>Ampliación</t>
-  </si>
-  <si>
-    <t>Continuación</t>
-  </si>
-  <si>
-    <t>Terracería</t>
-  </si>
-  <si>
-    <t>Andador</t>
-  </si>
-  <si>
-    <t>Periférico</t>
-  </si>
-  <si>
-    <t>Avenida</t>
-  </si>
-  <si>
-    <t>Aeropuerto</t>
-  </si>
-  <si>
-    <t>Barrio</t>
-  </si>
-  <si>
-    <t>Cantón</t>
-  </si>
-  <si>
     <t>Ciudad industrial</t>
   </si>
   <si>
@@ -953,28 +980,49 @@
     <t>Lugares donde se efectúa el pago</t>
   </si>
   <si>
-    <t>FB2115CFBB44014659556362896F385C</t>
+    <t>E621B4F9309A3370D09C1315C52A50AD</t>
   </si>
   <si>
     <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
   </si>
   <si>
-    <t>FB2115CFBB440146662F09D622F87A27</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5D71634BF23CE9C03</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146CB4D92342CB2037C</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF58267AE3A5603544D</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271324E4A5495145B89</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D127172234A927D7B31B0</t>
+    <t>E255390FE79E15E7DE6F257C3B4DCFA3</t>
+  </si>
+  <si>
+    <t>10E46DE8C1834182822BCCA8A2F87F13</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1B27A4C33E47076BB</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1EB0AD17645CFB784</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD12AB2728FFAAA20AD</t>
+  </si>
+  <si>
+    <t>E621B4F9309A3370BCD379BCC26E8A1C</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F82CB788827112EED15</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A243A86F8E388B5107</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C2C649CAB6A36577C</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C3FC5621BD2721BA3</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C4C6F56E97C447666</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F82A6FEA638EBA0CDDF</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A2EF168BC192028D76</t>
   </si>
   <si>
     <t>76320</t>
@@ -1046,25 +1094,46 @@
     <t>Código postal</t>
   </si>
   <si>
-    <t>FB2115CFBB440146337462A6C6073EB8</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146CAB0FD84B7C4B6DC</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF51300D1EC26EBE6EC</t>
-  </si>
-  <si>
-    <t>82BE20F1A5758727D49FBDFA09FFA573</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5CB4F5691590F89EA</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF519F29A68A3FA9A1F</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271E3731360E0A38DE8</t>
+    <t>E621B4F9309A3370FC2AFDE3244B47BA</t>
+  </si>
+  <si>
+    <t>E255390FE79E15E7C28634AD3F780F98</t>
+  </si>
+  <si>
+    <t>10E46DE8C1834182E5DBDC0D6399886E</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD18EADCEB5237A87D6</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1D199BCF3E1987AB0</t>
+  </si>
+  <si>
+    <t>E621B4F9309A33705252F50CE0AFAE6F</t>
+  </si>
+  <si>
+    <t>E621B4F9309A33702F331CF46C29C2A0</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F8256870F558CAD0267</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A20212D653A33F233A</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5CE313219D341D6792</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C5C64D2B9542FF337</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C030D5123EE3764C0</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F82A4EB3C9733F34825</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A224379AAB0CCF0A56</t>
   </si>
   <si>
     <t>56400</t>
@@ -1142,43 +1211,46 @@
     <t>Entidad federativa</t>
   </si>
   <si>
-    <t>FB2115CFBB44014674EA69810E255BE3</t>
-  </si>
-  <si>
-    <t>01 246 465 0900 Ext. 2113,2114,2139</t>
-  </si>
-  <si>
-    <t>se.honesto.ce@tlaxcala.gob.mx</t>
-  </si>
-  <si>
-    <t>Ex- Rancho la Aguanaja</t>
-  </si>
-  <si>
-    <t>Apetatitlán</t>
-  </si>
-  <si>
-    <t>Apetatitlán de Antonio Carvajal</t>
-  </si>
-  <si>
-    <t>90600</t>
-  </si>
-  <si>
-    <t>FB2115CFBB440146CC43F01B0074418B</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF53F3838359232C641</t>
-  </si>
-  <si>
-    <t>82BE20F1A57587273181E15556F81341</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF5F7B7CEDF8F2C84A9</t>
-  </si>
-  <si>
-    <t>DBBD92DEDB940DF582CB1B3CA2FD893D</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271FAC1E6E3B2D7C7BB</t>
+    <t>E621B4F9309A3370CA36DC10920334FF</t>
+  </si>
+  <si>
+    <t>E255390FE79E15E7088AB0D78E79A3B7</t>
+  </si>
+  <si>
+    <t>10E46DE8C18341822EE366FE04102360</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD16D42FC15CC196A3A</t>
+  </si>
+  <si>
+    <t>19816EBFD3BC4CD1D9FB1BE3E2DAAE19</t>
+  </si>
+  <si>
+    <t>E621B4F9309A33703FAD45952F26C312</t>
+  </si>
+  <si>
+    <t>E621B4F9309A33702D19697A954642FF</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F827FC6FB9D0204C820</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A2343506509A7E27AB</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C23FF1C91DA1BB0ED</t>
+  </si>
+  <si>
+    <t>49425D25BA776D5C5AF85C8388DEA98B</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F82D4C1D8C109D0FDCD</t>
+  </si>
+  <si>
+    <t>7CA601AF42FA1F82BC7B01BC63A747CC</t>
+  </si>
+  <si>
+    <t>EFC3E2D98D7322A26A742C30997C673D</t>
   </si>
 </sst>
 </file>
@@ -1577,29 +1649,29 @@
   <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="255" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="119.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="83.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="180" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="88.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="103.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="102.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="32.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="53.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="100.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="132" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="245" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="255" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="138" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="116.28515625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="47.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="78.7109375" bestFit="1" customWidth="1"/>
@@ -1949,646 +2021,646 @@
     </row>
     <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>82</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="W8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB8" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="S9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S9" s="3" t="s">
+      <c r="V9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB9" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB10" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="M11" s="3" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB11" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>111</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="S12" s="3" t="s">
+      <c r="T12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB12" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB13" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="AC13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD13" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="H14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="W14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB14" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="AD14" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2612,162 +2684,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -2777,12 +2849,12 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -2808,7 +2880,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" t="s">
         <v>8</v>
@@ -2820,7 +2892,7 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -2841,7 +2913,7 @@
         <v>8</v>
       </c>
       <c r="P1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q1" t="s">
         <v>8</v>
@@ -2852,498 +2924,890 @@
     </row>
     <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="E2" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="F2" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="G2" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="I2" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="J2" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="K2" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="L2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="M2" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="N2" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="O2" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="P2" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="Q2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="R2" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K4" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K6" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K7" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K8" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>367</v>
+        <v>203</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>368</v>
+        <v>204</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>92</v>
+      <c r="J17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3369,132 +3833,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3509,207 +3973,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3724,162 +4188,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3889,11 +4353,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="82.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -3919,7 +4383,7 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -3931,7 +4395,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
@@ -3952,7 +4416,7 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P1" t="s">
         <v>6</v>
@@ -3972,552 +4436,986 @@
     </row>
     <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="I16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="I17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="K17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="O17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="Q17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>194</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -4543,132 +5441,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4683,207 +5581,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -4898,162 +5796,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5063,11 +5961,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5078,93 +5976,170 @@
     </row>
     <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>304</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>304</v>
+      <c r="B16" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -5174,11 +6149,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -5203,7 +6178,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F1" t="s">
         <v>8</v>
@@ -5215,7 +6190,7 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -5236,7 +6211,7 @@
         <v>6</v>
       </c>
       <c r="P1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q1" t="s">
         <v>6</v>
@@ -5244,471 +6219,842 @@
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="G2" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="H2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="I2" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="K2" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="L2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="M2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="N2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="O2" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="P2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="Q2" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>85</v>
+      <c r="B16" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5734,132 +7080,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5874,207 +7220,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
